--- a/result/xlsx/mannwhitney1.xlsx
+++ b/result/xlsx/mannwhitney1.xlsx
@@ -14,17 +14,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>rat_number</t>
   </si>
   <si>
+    <t>LAS_ms_diff</t>
+  </si>
+  <si>
     <t>LAS_ms_pvalue</t>
   </si>
   <si>
     <t>LAS_ms_significant</t>
   </si>
   <si>
+    <t>LAS_ms_statistic</t>
+  </si>
+  <si>
     <t>QRSoff_diff</t>
   </si>
   <si>
@@ -49,10 +55,16 @@
     <t>QRSon_statistic</t>
   </si>
   <si>
+    <t>RMS40_mkV_diff</t>
+  </si>
+  <si>
     <t>RMS40_mkV_pvalue</t>
   </si>
   <si>
     <t>RMS40_mkV_significant</t>
+  </si>
+  <si>
+    <t>RMS40_mkV_statistic</t>
   </si>
   <si>
     <t>fQRS_ms_diff</t>
@@ -468,10 +480,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AS10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:41">
+    <row r="1" spans="1:45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -595,1021 +607,1249 @@
       <c r="AO1" t="s">
         <v>40</v>
       </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:45">
       <c r="A2">
         <v>10</v>
       </c>
-      <c r="D2">
+      <c r="B2">
+        <v>-8.480000000000004</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>-53</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>-4</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
       <c r="K2">
         <v>1</v>
       </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
       <c r="N2">
+        <v>-0.02643997486758689</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
         <v>-7.840000000000003</v>
       </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
         <v>-7.428063719475066</v>
       </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>1</v>
-      </c>
-      <c r="V2">
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
         <v>-0.001233328463409987</v>
       </c>
-      <c r="W2">
-        <v>1</v>
-      </c>
-      <c r="X2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>1</v>
-      </c>
-      <c r="Z2">
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
         <v>0.001170456041810392</v>
       </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
         <v>-7.322282204836982E-05</v>
       </c>
-      <c r="AE2">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>1</v>
-      </c>
-      <c r="AH2">
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
         <v>1.902572877185887</v>
       </c>
-      <c r="AI2">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
+      <c r="AM2">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
         <v>-0.01568296578219567</v>
       </c>
-      <c r="AM2">
-        <v>1</v>
-      </c>
-      <c r="AN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO2">
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:45">
       <c r="A3">
         <v>11</v>
       </c>
-      <c r="D3">
+      <c r="B3">
+        <v>-16.32</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>-102</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
         <v>-89</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
       <c r="K3">
         <v>1</v>
       </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
       <c r="N3">
+        <v>-0.02387887830787989</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
         <v>-2.080000000000002</v>
       </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
         <v>-8.385768775763017</v>
       </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
-      <c r="V3">
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>1</v>
+      </c>
+      <c r="Z3">
         <v>0.0007782565808294791</v>
       </c>
-      <c r="W3">
-        <v>1</v>
-      </c>
-      <c r="X3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
         <v>-0.7686531922280156</v>
       </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>1</v>
-      </c>
-      <c r="AD3">
+      <c r="AE3">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>1</v>
+      </c>
+      <c r="AH3">
         <v>-0.8467447229627747</v>
       </c>
-      <c r="AE3">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>1</v>
-      </c>
-      <c r="AH3">
+      <c r="AI3">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>1</v>
+      </c>
+      <c r="AL3">
         <v>-0.8240394328119671</v>
       </c>
-      <c r="AI3">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>1</v>
-      </c>
-      <c r="AL3">
+      <c r="AM3">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>1</v>
+      </c>
+      <c r="AP3">
         <v>0.02315734509653354</v>
       </c>
-      <c r="AM3">
-        <v>1</v>
-      </c>
-      <c r="AN3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO3">
+      <c r="AQ3">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:45">
       <c r="A4">
         <v>12</v>
       </c>
-      <c r="D4">
+      <c r="B4">
+        <v>11.67999999999999</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>73</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>-10</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
       <c r="K4">
         <v>1</v>
       </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
       <c r="N4">
+        <v>-0.009781868006380704</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
         <v>13.28</v>
       </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
         <v>-4.851336794649722</v>
       </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="V4">
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
         <v>-0.001466557836253024</v>
       </c>
-      <c r="W4">
-        <v>1</v>
-      </c>
-      <c r="X4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>1</v>
-      </c>
-      <c r="Z4">
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
         <v>-0.0009633945817365333</v>
       </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>1</v>
-      </c>
-      <c r="AD4">
+      <c r="AE4">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
+      <c r="AH4">
         <v>-4.139716079630879E-05</v>
       </c>
-      <c r="AE4">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>1</v>
-      </c>
-      <c r="AH4">
+      <c r="AI4">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>1</v>
+      </c>
+      <c r="AL4">
         <v>2.190465152638862</v>
       </c>
-      <c r="AI4">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
+      <c r="AM4">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
         <v>0.005405556973263358</v>
       </c>
-      <c r="AM4">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO4">
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:45">
       <c r="A5">
         <v>13</v>
       </c>
-      <c r="D5">
+      <c r="B5">
+        <v>-140</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>-875</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>-66</v>
       </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
       <c r="K5">
         <v>1</v>
       </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
       <c r="N5">
+        <v>0.005274154686460831</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
         <v>-129.44</v>
       </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
         <v>-9.975848223591267</v>
       </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5">
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
         <v>-0.001042494512213162</v>
       </c>
-      <c r="W5">
-        <v>1</v>
-      </c>
-      <c r="X5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>1</v>
-      </c>
-      <c r="Z5">
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
         <v>0.03063664225459406</v>
       </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
+      <c r="AE5">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
         <v>0.008087124353508911</v>
       </c>
-      <c r="AE5">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
         <v>2.959568814626711</v>
       </c>
-      <c r="AI5">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
+      <c r="AM5">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
         <v>-0.001915609659054155</v>
       </c>
-      <c r="AM5">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO5">
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:45">
       <c r="A6">
         <v>14</v>
       </c>
-      <c r="D6">
+      <c r="B6">
+        <v>-42.88</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>-268</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
       <c r="G6">
         <v>1</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>-96</v>
       </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
       <c r="K6">
         <v>1</v>
       </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
       <c r="N6">
+        <v>0.01328907054956092</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
         <v>-27.52000000000002</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
         <v>-4.149025457436361</v>
       </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>1</v>
-      </c>
-      <c r="V6">
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
         <v>-0.00328753057532857</v>
       </c>
-      <c r="W6">
-        <v>1</v>
-      </c>
-      <c r="X6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>1</v>
-      </c>
-      <c r="Z6">
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
         <v>0.00075543950625864</v>
       </c>
-      <c r="AA6">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
         <v>8.151951435353416E-05</v>
       </c>
-      <c r="AE6">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
         <v>-0.135428011929361</v>
       </c>
-      <c r="AI6">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>1</v>
-      </c>
-      <c r="AL6">
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
         <v>-0.001333223427788147</v>
       </c>
-      <c r="AM6">
-        <v>1</v>
-      </c>
-      <c r="AN6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO6">
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:45">
       <c r="A7">
         <v>15</v>
       </c>
-      <c r="D7">
+      <c r="B7">
+        <v>-37.76000000000001</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>-236</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
       <c r="G7">
         <v>1</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
         <v>16</v>
       </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
       <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
+        <v>0.00532122228705763</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
         <v>-40.31999999999999</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
         <v>-1.835737365399734</v>
       </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="V7">
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
         <v>-0.001375933252267968</v>
       </c>
-      <c r="W7">
-        <v>1</v>
-      </c>
-      <c r="X7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>1</v>
-      </c>
-      <c r="Z7">
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
         <v>0.0003012829893713407</v>
       </c>
-      <c r="AA7">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
+      <c r="AE7">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
         <v>-8.284371050249867E-05</v>
       </c>
-      <c r="AE7">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>1</v>
-      </c>
-      <c r="AH7">
+      <c r="AI7">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>1</v>
+      </c>
+      <c r="AL7">
         <v>0.2037726353071061</v>
       </c>
-      <c r="AI7">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
         <v>-0.0008146718330896141</v>
       </c>
-      <c r="AM7">
-        <v>1</v>
-      </c>
-      <c r="AN7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO7">
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:45">
       <c r="A8">
         <v>16</v>
       </c>
-      <c r="D8">
+      <c r="B8">
+        <v>0.6400000000000006</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>4</v>
       </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
       <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
         <v>20</v>
       </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
       <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
+        <v>-0.01936381290446237</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
         <v>-2.559999999999999</v>
       </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
         <v>-2.062239121363882</v>
       </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8">
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
         <v>-0.0002791812836260661</v>
       </c>
-      <c r="W8">
-        <v>1</v>
-      </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>1</v>
-      </c>
-      <c r="Z8">
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
         <v>0.001290600457468179</v>
       </c>
-      <c r="AA8">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
         <v>-9.42040206766892E-05</v>
       </c>
-      <c r="AE8">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>1</v>
-      </c>
-      <c r="AH8">
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
         <v>-0.2174348877288359</v>
       </c>
-      <c r="AI8">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>1</v>
-      </c>
-      <c r="AL8">
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
         <v>-0.004620082497114927</v>
       </c>
-      <c r="AM8">
-        <v>1</v>
-      </c>
-      <c r="AN8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO8">
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:45">
       <c r="A9">
         <v>17</v>
       </c>
-      <c r="D9">
+      <c r="B9">
+        <v>-69.44000000000001</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
         <v>-434</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
       <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
         <v>10</v>
       </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
       <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
+        <v>0.01312610725086467</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
         <v>-71.04000000000001</v>
       </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
         <v>-1.515920684185946</v>
       </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="V9">
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
         <v>0.0001692883373975815</v>
       </c>
-      <c r="W9">
-        <v>1</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
         <v>2.555533297400467E-05</v>
       </c>
-      <c r="AA9">
-        <v>1</v>
-      </c>
-      <c r="AB9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
         <v>2.474698849722013E-05</v>
       </c>
-      <c r="AE9">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AH9">
+      <c r="AI9">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
         <v>0.3672662306781732</v>
       </c>
-      <c r="AI9">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK9">
-        <v>0</v>
-      </c>
-      <c r="AL9">
+      <c r="AM9">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
         <v>0.01492972267342793</v>
       </c>
-      <c r="AM9">
-        <v>1</v>
-      </c>
-      <c r="AN9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO9">
+      <c r="AQ9">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:41">
+    <row r="10" spans="1:45">
       <c r="A10">
         <v>18</v>
       </c>
-      <c r="D10">
+      <c r="B10">
+        <v>3.040000000000006</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>19</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
       <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
         <v>-7</v>
       </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
       <c r="K10">
         <v>1</v>
       </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
       <c r="N10">
+        <v>-0.02041413791761553</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
         <v>4.16</v>
       </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
         <v>0.7480822238755938</v>
       </c>
-      <c r="S10">
-        <v>1</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
         <v>6.7341505454251E-05</v>
       </c>
-      <c r="W10">
-        <v>1</v>
-      </c>
-      <c r="X10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
         <v>-0.0002898121301966503</v>
       </c>
-      <c r="AA10">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>1</v>
-      </c>
-      <c r="AD10">
+      <c r="AE10">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>1</v>
+      </c>
+      <c r="AH10">
         <v>-4.153616872257381E-05</v>
       </c>
-      <c r="AE10">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>1</v>
-      </c>
-      <c r="AH10">
+      <c r="AI10">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>1</v>
+      </c>
+      <c r="AL10">
         <v>0.3479920255210545</v>
       </c>
-      <c r="AI10">
-        <v>1</v>
-      </c>
-      <c r="AJ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK10">
-        <v>0</v>
-      </c>
-      <c r="AL10">
+      <c r="AM10">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
         <v>-0.01942736403852773</v>
       </c>
-      <c r="AM10">
-        <v>1</v>
-      </c>
-      <c r="AN10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO10">
+      <c r="AQ10">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10">
         <v>1</v>
       </c>
     </row>

--- a/result/xlsx/mannwhitney1.xlsx
+++ b/result/xlsx/mannwhitney1.xlsx
@@ -480,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AS3"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:45">
@@ -622,10 +622,10 @@
     </row>
     <row r="2" spans="1:45">
       <c r="A2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>-69.44000000000001</v>
+        <v>0.6400000000000006</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -634,10 +634,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>-434</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -646,10 +646,10 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.01312610725086467</v>
+        <v>-0.01936381290446237</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -670,10 +670,10 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>-71.04000000000001</v>
+        <v>-2.559999999999999</v>
       </c>
       <c r="S2">
         <v>1</v>
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="V2">
-        <v>-1.515920684185946</v>
+        <v>-2.062239121363882</v>
       </c>
       <c r="W2">
         <v>1</v>
@@ -697,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>0.0001692883373975815</v>
+        <v>-0.0002791812836260661</v>
       </c>
       <c r="AA2">
         <v>1</v>
@@ -706,10 +706,10 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2">
-        <v>2.555533297400467E-05</v>
+        <v>0.001290600457468179</v>
       </c>
       <c r="AE2">
         <v>1</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="AH2">
-        <v>2.474698849722013E-05</v>
+        <v>-9.42040206766892E-05</v>
       </c>
       <c r="AI2">
         <v>1</v>
@@ -730,10 +730,10 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL2">
-        <v>0.3672662306781732</v>
+        <v>-0.2174348877288359</v>
       </c>
       <c r="AM2">
         <v>1</v>
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP2">
-        <v>0.01492972267342793</v>
+        <v>-0.004620082497114927</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -754,143 +754,280 @@
         <v>0</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:45">
       <c r="A3">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>-69.44000000000001</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>-434</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0.01312610725086467</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>-71.04000000000001</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>-1.515920684185946</v>
+      </c>
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>1</v>
+      </c>
+      <c r="Z3">
+        <v>0.0001692883373975815</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>2.555533297400467E-05</v>
+      </c>
+      <c r="AE3">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>2.474698849722013E-05</v>
+      </c>
+      <c r="AI3">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0.3672662306781732</v>
+      </c>
+      <c r="AM3">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0.01492972267342793</v>
+      </c>
+      <c r="AQ3">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:45">
+      <c r="A4">
         <v>18</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>3.040000000000006</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>19</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>-7</v>
       </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
         <v>-0.02041413791761553</v>
       </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
         <v>4.16</v>
       </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
         <v>0.7480822238755938</v>
       </c>
-      <c r="W3">
-        <v>1</v>
-      </c>
-      <c r="X3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
         <v>6.7341505454251E-05</v>
       </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
         <v>-0.0002898121301966503</v>
       </c>
-      <c r="AE3">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>1</v>
-      </c>
-      <c r="AH3">
+      <c r="AE4">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
+      <c r="AH4">
         <v>-4.153616872257381E-05</v>
       </c>
-      <c r="AI3">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>1</v>
-      </c>
-      <c r="AL3">
+      <c r="AI4">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>1</v>
+      </c>
+      <c r="AL4">
         <v>0.3479920255210545</v>
       </c>
-      <c r="AM3">
-        <v>1</v>
-      </c>
-      <c r="AN3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
+      <c r="AM4">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
         <v>-0.01942736403852773</v>
       </c>
-      <c r="AQ3">
-        <v>1</v>
-      </c>
-      <c r="AR3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS3">
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4">
         <v>1</v>
       </c>
     </row>

--- a/result/xlsx/mannwhitney1.xlsx
+++ b/result/xlsx/mannwhitney1.xlsx
@@ -480,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AS4"/>
+  <dimension ref="A1:AS10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:45">
@@ -622,10 +622,10 @@
     </row>
     <row r="2" spans="1:45">
       <c r="A2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>0.6400000000000006</v>
+        <v>-8.480000000000004</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -634,10 +634,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>-53</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -646,10 +646,10 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>20</v>
+        <v>-4</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>-0.01936381290446237</v>
+        <v>-0.02643997486758689</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -673,7 +673,7 @@
         <v>1</v>
       </c>
       <c r="R2">
-        <v>-2.559999999999999</v>
+        <v>-7.840000000000003</v>
       </c>
       <c r="S2">
         <v>1</v>
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="V2">
-        <v>-2.062239121363882</v>
+        <v>-7.428063719475066</v>
       </c>
       <c r="W2">
         <v>1</v>
@@ -697,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>-0.0002791812836260661</v>
+        <v>-0.001233328463409987</v>
       </c>
       <c r="AA2">
         <v>1</v>
@@ -709,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="AD2">
-        <v>0.001290600457468179</v>
+        <v>0.001170456041810392</v>
       </c>
       <c r="AE2">
         <v>1</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="AH2">
-        <v>-9.42040206766892E-05</v>
+        <v>-7.322282204836982E-05</v>
       </c>
       <c r="AI2">
         <v>1</v>
@@ -733,7 +733,7 @@
         <v>1</v>
       </c>
       <c r="AL2">
-        <v>-0.2174348877288359</v>
+        <v>1.902572877185887</v>
       </c>
       <c r="AM2">
         <v>1</v>
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.004620082497114927</v>
+        <v>-0.01568296578219567</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="3" spans="1:45">
       <c r="A3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3">
-        <v>-69.44000000000001</v>
+        <v>-16.32</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -774,7 +774,7 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>-434</v>
+        <v>-102</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -786,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>-89</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -795,10 +795,10 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>0.01312610725086467</v>
+        <v>-0.02387887830787989</v>
       </c>
       <c r="O3">
         <v>1</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>-71.04000000000001</v>
+        <v>-2.080000000000002</v>
       </c>
       <c r="S3">
         <v>1</v>
@@ -822,7 +822,7 @@
         <v>1</v>
       </c>
       <c r="V3">
-        <v>-1.515920684185946</v>
+        <v>-8.385768775763017</v>
       </c>
       <c r="W3">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>0.0001692883373975815</v>
+        <v>0.0007782565808294791</v>
       </c>
       <c r="AA3">
         <v>1</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>2.555533297400467E-05</v>
+        <v>-0.7686531922280156</v>
       </c>
       <c r="AE3">
         <v>1</v>
@@ -855,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH3">
-        <v>2.474698849722013E-05</v>
+        <v>-0.8467447229627747</v>
       </c>
       <c r="AI3">
         <v>1</v>
@@ -867,10 +867,10 @@
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL3">
-        <v>0.3672662306781732</v>
+        <v>-0.8240394328119671</v>
       </c>
       <c r="AM3">
         <v>1</v>
@@ -879,10 +879,10 @@
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3">
-        <v>0.01492972267342793</v>
+        <v>0.02315734509653354</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -896,138 +896,960 @@
     </row>
     <row r="4" spans="1:45">
       <c r="A4">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>11.67999999999999</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>73</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>-10</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>-0.009781868006380704</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>13.28</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>-4.851336794649722</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>-0.001466557836253024</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>-0.0009633945817365333</v>
+      </c>
+      <c r="AE4">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <v>-4.139716079630879E-05</v>
+      </c>
+      <c r="AI4">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <v>2.190465152638862</v>
+      </c>
+      <c r="AM4">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0.005405556973263358</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:45">
+      <c r="A5">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>-140</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>-875</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>-66</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0.005274154686460831</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>-129.44</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>-9.975848223591267</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>-0.001042494512213162</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>0.03063664225459406</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0.008087124353508911</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>2.959568814626711</v>
+      </c>
+      <c r="AM5">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>-0.001915609659054155</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45">
+      <c r="A6">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>-42.88</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>-268</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>-96</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0.01328907054956092</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>-27.52000000000002</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>-4.149025457436361</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>-0.00328753057532857</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>0.00075543950625864</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>8.151951435353416E-05</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>-0.135428011929361</v>
+      </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>-0.001333223427788147</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:45">
+      <c r="A7">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>-37.76000000000001</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>-236</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>16</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0.00532122228705763</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>-40.31999999999999</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>-1.835737365399734</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>-0.001375933252267968</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>0.0003012829893713407</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>-8.284371050249867E-05</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <v>0.2037726353071061</v>
+      </c>
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>-0.0008146718330896141</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45">
+      <c r="A8">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>0.6400000000000006</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>-0.01936381290446237</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>-2.559999999999999</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>-2.062239121363882</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>-0.0002791812836260661</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>0.001290600457468179</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>-9.42040206766892E-05</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>-0.2174348877288359</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>-0.004620082497114927</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:45">
+      <c r="A9">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>-69.44000000000001</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>-434</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0.01312610725086467</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>-71.04000000000001</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>-1.515920684185946</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>0.0001692883373975815</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>2.555533297400467E-05</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>2.474698849722013E-05</v>
+      </c>
+      <c r="AI9">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0.3672662306781732</v>
+      </c>
+      <c r="AM9">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0.01492972267342793</v>
+      </c>
+      <c r="AQ9">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:45">
+      <c r="A10">
         <v>18</v>
       </c>
-      <c r="B4">
+      <c r="B10">
         <v>3.040000000000006</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>19</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
         <v>-7</v>
       </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
         <v>-0.02041413791761553</v>
       </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
         <v>4.16</v>
       </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
         <v>0.7480822238755938</v>
       </c>
-      <c r="W4">
-        <v>1</v>
-      </c>
-      <c r="X4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
         <v>6.7341505454251E-05</v>
       </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
         <v>-0.0002898121301966503</v>
       </c>
-      <c r="AE4">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>1</v>
-      </c>
-      <c r="AH4">
+      <c r="AE10">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>1</v>
+      </c>
+      <c r="AH10">
         <v>-4.153616872257381E-05</v>
       </c>
-      <c r="AI4">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>1</v>
-      </c>
-      <c r="AL4">
+      <c r="AI10">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>1</v>
+      </c>
+      <c r="AL10">
         <v>0.3479920255210545</v>
       </c>
-      <c r="AM4">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
+      <c r="AM10">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
         <v>-0.01942736403852773</v>
       </c>
-      <c r="AQ4">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS4">
+      <c r="AQ10">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10">
         <v>1</v>
       </c>
     </row>

--- a/result/xlsx/mannwhitney1.xlsx
+++ b/result/xlsx/mannwhitney1.xlsx
@@ -625,7 +625,7 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>-8.480000000000004</v>
+        <v>-8.319999999999993</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -637,7 +637,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>-53</v>
+        <v>-52</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -649,7 +649,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -661,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>-0.02643997486758689</v>
+        <v>-0.026683770405171</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -673,7 +673,7 @@
         <v>1</v>
       </c>
       <c r="R2">
-        <v>-7.840000000000003</v>
+        <v>-7.52</v>
       </c>
       <c r="S2">
         <v>1</v>
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="V2">
-        <v>-7.428063719475066</v>
+        <v>-6.950197553260211</v>
       </c>
       <c r="W2">
         <v>1</v>
@@ -697,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>-0.001233328463409987</v>
+        <v>-0.001262234737359428</v>
       </c>
       <c r="AA2">
         <v>1</v>
@@ -709,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="AD2">
-        <v>0.001170456041810392</v>
+        <v>0.0005235194462570993</v>
       </c>
       <c r="AE2">
         <v>1</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="AH2">
-        <v>-7.322282204836982E-05</v>
+        <v>-8.233442023367387E-05</v>
       </c>
       <c r="AI2">
         <v>1</v>
@@ -733,7 +733,7 @@
         <v>1</v>
       </c>
       <c r="AL2">
-        <v>1.902572877185887</v>
+        <v>1.820934419146435</v>
       </c>
       <c r="AM2">
         <v>1</v>
@@ -745,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.01568296578219567</v>
+        <v>-0.01786072574616755</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -762,7 +762,7 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>-16.32</v>
+        <v>-85.44000000000001</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -774,7 +774,7 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>-102</v>
+        <v>-534</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -786,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>-89</v>
+        <v>-245</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>-0.02387887830787989</v>
+        <v>0.01682587886162912</v>
       </c>
       <c r="O3">
         <v>1</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>-2.080000000000002</v>
+        <v>-46.24</v>
       </c>
       <c r="S3">
         <v>1</v>
@@ -822,7 +822,7 @@
         <v>1</v>
       </c>
       <c r="V3">
-        <v>-8.385768775763017</v>
+        <v>-8.655057744105017</v>
       </c>
       <c r="W3">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>0.0007782565808294791</v>
+        <v>0.0008715358946342784</v>
       </c>
       <c r="AA3">
         <v>1</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>-0.7686531922280156</v>
+        <v>-0.7750574319232306</v>
       </c>
       <c r="AE3">
         <v>1</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="AH3">
-        <v>-0.8467447229627747</v>
+        <v>-0.8573637427170601</v>
       </c>
       <c r="AI3">
         <v>1</v>
@@ -870,7 +870,7 @@
         <v>1</v>
       </c>
       <c r="AL3">
-        <v>-0.8240394328119671</v>
+        <v>-1.059312641950133</v>
       </c>
       <c r="AM3">
         <v>1</v>
@@ -882,7 +882,7 @@
         <v>1</v>
       </c>
       <c r="AP3">
-        <v>0.02315734509653354</v>
+        <v>0.02772932060397213</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -899,7 +899,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>11.67999999999999</v>
+        <v>12.31999999999999</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>-10</v>
+        <v>-199</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -935,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>-0.009781868006380704</v>
+        <v>-0.007285932224088475</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="R4">
-        <v>13.28</v>
+        <v>44.16</v>
       </c>
       <c r="S4">
         <v>1</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="V4">
-        <v>-4.851336794649722</v>
+        <v>-5.177205692845613</v>
       </c>
       <c r="W4">
         <v>1</v>
@@ -971,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>-0.001466557836253024</v>
+        <v>-0.0009659508847740837</v>
       </c>
       <c r="AA4">
         <v>1</v>
@@ -983,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="AD4">
-        <v>-0.0009633945817365333</v>
+        <v>-0.0009902184076204712</v>
       </c>
       <c r="AE4">
         <v>1</v>
@@ -995,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="AH4">
-        <v>-4.139716079630879E-05</v>
+        <v>-6.003005148603603E-05</v>
       </c>
       <c r="AI4">
         <v>1</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="AL4">
-        <v>2.190465152638862</v>
+        <v>2.143111690983203</v>
       </c>
       <c r="AM4">
         <v>1</v>
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.005405556973263358</v>
+        <v>0.01190508870906307</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-140</v>
+        <v>-80.96000000000001</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>-875</v>
+        <v>-506</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1060,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>-66</v>
+        <v>-35</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>0.005274154686460831</v>
+        <v>0.0009546940005462864</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>-129.44</v>
+        <v>-75.36</v>
       </c>
       <c r="S5">
         <v>1</v>
@@ -1096,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="V5">
-        <v>-9.975848223591267</v>
+        <v>-8.469750533954814</v>
       </c>
       <c r="W5">
         <v>1</v>
@@ -1108,7 +1108,7 @@
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>-0.001042494512213162</v>
+        <v>-0.002747698913383587</v>
       </c>
       <c r="AA5">
         <v>1</v>
@@ -1120,7 +1120,7 @@
         <v>1</v>
       </c>
       <c r="AD5">
-        <v>0.03063664225459406</v>
+        <v>0.04323335584004028</v>
       </c>
       <c r="AE5">
         <v>1</v>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="AH5">
-        <v>0.008087124353508911</v>
+        <v>0.01200484972704805</v>
       </c>
       <c r="AI5">
         <v>1</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="AL5">
-        <v>2.959568814626711</v>
+        <v>2.031652990253252</v>
       </c>
       <c r="AM5">
         <v>1</v>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>-0.001915609659054155</v>
+        <v>-0.0009262248184164455</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -1173,7 +1173,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-42.88</v>
+        <v>-33.44000000000001</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1185,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>-268</v>
+        <v>-209</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1197,7 +1197,7 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>-96</v>
+        <v>-7</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1209,7 +1209,7 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>0.01328907054956092</v>
+        <v>0.02184955521689701</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>-27.52000000000002</v>
+        <v>-32.31999999999999</v>
       </c>
       <c r="S6">
         <v>1</v>
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="V6">
-        <v>-4.149025457436361</v>
+        <v>-1.219905320152815</v>
       </c>
       <c r="W6">
         <v>1</v>
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>-0.00328753057532857</v>
+        <v>-0.002998787943384183</v>
       </c>
       <c r="AA6">
         <v>1</v>
@@ -1257,7 +1257,7 @@
         <v>1</v>
       </c>
       <c r="AD6">
-        <v>0.00075543950625864</v>
+        <v>0.0005354105403268484</v>
       </c>
       <c r="AE6">
         <v>1</v>
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="AH6">
-        <v>8.151951435353416E-05</v>
+        <v>5.935692280085025E-05</v>
       </c>
       <c r="AI6">
         <v>1</v>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="AL6">
-        <v>-0.135428011929361</v>
+        <v>1.436690419659338</v>
       </c>
       <c r="AM6">
         <v>1</v>
@@ -1290,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="AO6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP6">
-        <v>-0.001333223427788147</v>
+        <v>0.005037305764430466</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="AS6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:45">
@@ -1310,7 +1310,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-37.76000000000001</v>
+        <v>2.079999999999998</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1319,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>-236</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1331,10 +1331,10 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.00532122228705763</v>
+        <v>-0.01682795570984305</v>
       </c>
       <c r="O7">
         <v>1</v>
@@ -1355,10 +1355,10 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>-40.31999999999999</v>
+        <v>-1.120000000000001</v>
       </c>
       <c r="S7">
         <v>1</v>
@@ -1370,7 +1370,7 @@
         <v>1</v>
       </c>
       <c r="V7">
-        <v>-1.835737365399734</v>
+        <v>-2.33485084159987</v>
       </c>
       <c r="W7">
         <v>1</v>
@@ -1382,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>-0.001375933252267968</v>
+        <v>-0.000924705653329028</v>
       </c>
       <c r="AA7">
         <v>1</v>
@@ -1394,7 +1394,7 @@
         <v>1</v>
       </c>
       <c r="AD7">
-        <v>0.0003012829893713407</v>
+        <v>0.0008031168779460421</v>
       </c>
       <c r="AE7">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>-8.284371050249867E-05</v>
+        <v>-8.608954442493582E-05</v>
       </c>
       <c r="AI7">
         <v>1</v>
@@ -1418,7 +1418,7 @@
         <v>1</v>
       </c>
       <c r="AL7">
-        <v>0.2037726353071061</v>
+        <v>0.1948039163837394</v>
       </c>
       <c r="AM7">
         <v>1</v>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>-0.0008146718330896141</v>
+        <v>-0.001314829015341214</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -1447,7 +1447,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>0.6400000000000006</v>
+        <v>3.359999999999999</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1471,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>20</v>
+        <v>-40</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1480,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>-0.01936381290446237</v>
+        <v>-0.02113016030444858</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -1495,7 +1495,7 @@
         <v>1</v>
       </c>
       <c r="R8">
-        <v>-2.559999999999999</v>
+        <v>9.759999999999998</v>
       </c>
       <c r="S8">
         <v>1</v>
@@ -1504,10 +1504,10 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>-2.062239121363882</v>
+        <v>-2.448868495021888</v>
       </c>
       <c r="W8">
         <v>1</v>
@@ -1519,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-0.0002791812836260661</v>
+        <v>-0.0002832624583287473</v>
       </c>
       <c r="AA8">
         <v>1</v>
@@ -1531,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="AD8">
-        <v>0.001290600457468179</v>
+        <v>0.00251394881424729</v>
       </c>
       <c r="AE8">
         <v>1</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="AH8">
-        <v>-9.42040206766892E-05</v>
+        <v>-6.061220302007185E-05</v>
       </c>
       <c r="AI8">
         <v>1</v>
@@ -1555,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="AL8">
-        <v>-0.2174348877288359</v>
+        <v>-0.2522290304067533</v>
       </c>
       <c r="AM8">
         <v>1</v>
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="AP8">
-        <v>-0.004620082497114927</v>
+        <v>-0.001680074546032743</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -1584,7 +1584,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-69.44000000000001</v>
+        <v>-70.23999999999999</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>-434</v>
+        <v>-439</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1608,7 +1608,7 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>10</v>
+        <v>-18</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9">
-        <v>0.01312610725086467</v>
+        <v>0.01333969709580018</v>
       </c>
       <c r="O9">
         <v>1</v>
@@ -1632,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>-71.04000000000001</v>
+        <v>-67.35999999999999</v>
       </c>
       <c r="S9">
         <v>1</v>
@@ -1644,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="V9">
-        <v>-1.515920684185946</v>
+        <v>-2.098050453637971</v>
       </c>
       <c r="W9">
         <v>1</v>
@@ -1656,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>0.0001692883373975815</v>
+        <v>-0.0002040096985482479</v>
       </c>
       <c r="AA9">
         <v>1</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9">
-        <v>2.555533297400467E-05</v>
+        <v>0.0002912886673578729</v>
       </c>
       <c r="AE9">
         <v>1</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AH9">
-        <v>2.474698849722013E-05</v>
+        <v>2.222510236354745E-05</v>
       </c>
       <c r="AI9">
         <v>1</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="AL9">
-        <v>0.3672662306781732</v>
+        <v>0.08458292921320021</v>
       </c>
       <c r="AM9">
         <v>1</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.01492972267342793</v>
+        <v>0.01498767290497331</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -1721,7 +1721,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>3.040000000000006</v>
+        <v>14.24000000000001</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1757,7 +1757,7 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>-0.02041413791761553</v>
+        <v>-0.02160287670242469</v>
       </c>
       <c r="O10">
         <v>1</v>
@@ -1769,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="R10">
-        <v>4.16</v>
+        <v>16.64</v>
       </c>
       <c r="S10">
         <v>1</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="V10">
-        <v>0.7480822238755938</v>
+        <v>0.5193910154056312</v>
       </c>
       <c r="W10">
         <v>1</v>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>6.7341505454251E-05</v>
+        <v>-0.0001529639136833491</v>
       </c>
       <c r="AA10">
         <v>1</v>
@@ -1802,10 +1802,10 @@
         <v>0</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10">
-        <v>-0.0002898121301966503</v>
+        <v>0.0004979516193101001</v>
       </c>
       <c r="AE10">
         <v>1</v>
@@ -1814,10 +1814,10 @@
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>-4.153616872257381E-05</v>
+        <v>-4.136917679525396E-05</v>
       </c>
       <c r="AI10">
         <v>1</v>
@@ -1829,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="AL10">
-        <v>0.3479920255210545</v>
+        <v>0.2589928973243298</v>
       </c>
       <c r="AM10">
         <v>1</v>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>-0.01942736403852773</v>
+        <v>-0.01922309105697147</v>
       </c>
       <c r="AQ10">
         <v>1</v>

--- a/result/xlsx/mannwhitney1.xlsx
+++ b/result/xlsx/mannwhitney1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>metric</t>
   </si>
@@ -73,10 +73,19 @@
     <t>mean</t>
   </si>
   <si>
+    <t>permutation_entropy</t>
+  </si>
+  <si>
+    <t>phase_instability</t>
+  </si>
+  <si>
     <t>ratio_cwt_power</t>
   </si>
   <si>
     <t>ratio_psd_power</t>
+  </si>
+  <si>
+    <t>shannon_entropy</t>
   </si>
   <si>
     <t>skewness</t>
@@ -414,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -732,28 +741,28 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>0.001144086673244057</v>
+        <v>1.174853803563651</v>
       </c>
       <c r="E9">
-        <v>0.001881086486130078</v>
+        <v>1.203740639847587</v>
       </c>
       <c r="F9">
-        <v>0.000736999812886021</v>
+        <v>0.02888683628393629</v>
       </c>
       <c r="G9">
-        <v>0.08732116764256036</v>
+        <v>1.320328930749395</v>
       </c>
       <c r="H9">
-        <v>0.006471272250853074</v>
+        <v>1.266064137598739</v>
       </c>
       <c r="I9">
-        <v>-0.08084989539170728</v>
+        <v>-0.05426479315065591</v>
       </c>
       <c r="J9">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K9">
-        <v>0.331387096247615</v>
+        <v>0.7239320396139757</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -770,28 +779,28 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>6.636005579377209E-05</v>
+        <v>-0.1264858932598404</v>
       </c>
       <c r="E10">
-        <v>7.643116879641553E-06</v>
+        <v>-0.5966701504409082</v>
       </c>
       <c r="F10">
-        <v>-5.871693891413054E-05</v>
+        <v>-0.4701842571810678</v>
       </c>
       <c r="G10">
-        <v>0.09534153771936786</v>
+        <v>-0.1930557036416016</v>
       </c>
       <c r="H10">
-        <v>0.001385121457055902</v>
+        <v>-0.356179393534465</v>
       </c>
       <c r="I10">
-        <v>-0.09395641626231196</v>
+        <v>-0.1631236898928634</v>
       </c>
       <c r="J10">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="K10">
-        <v>0.2893148323819877</v>
+        <v>0.5364994693194564</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -808,28 +817,28 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>-0.5014526124883201</v>
+        <v>0.001144086673244057</v>
       </c>
       <c r="E11">
-        <v>-0.4848049280043791</v>
+        <v>0.001881086486130078</v>
       </c>
       <c r="F11">
-        <v>0.01664768448394099</v>
+        <v>0.000736999812886021</v>
       </c>
       <c r="G11">
-        <v>-0.8680898766780916</v>
+        <v>0.08732116764256036</v>
       </c>
       <c r="H11">
-        <v>-0.1281756999440235</v>
+        <v>0.006471272250853074</v>
       </c>
       <c r="I11">
-        <v>0.739914176734068</v>
+        <v>-0.08084989539170728</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K11">
-        <v>0.4799286921459572</v>
+        <v>0.331387096247615</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -846,30 +855,144 @@
         <v>9</v>
       </c>
       <c r="D12">
+        <v>6.636005579377209E-05</v>
+      </c>
+      <c r="E12">
+        <v>7.643116879641553E-06</v>
+      </c>
+      <c r="F12">
+        <v>-5.871693891413054E-05</v>
+      </c>
+      <c r="G12">
+        <v>0.09534153771936786</v>
+      </c>
+      <c r="H12">
+        <v>0.001385121457055902</v>
+      </c>
+      <c r="I12">
+        <v>-0.09395641626231196</v>
+      </c>
+      <c r="J12">
+        <v>53</v>
+      </c>
+      <c r="K12">
+        <v>0.2893148323819877</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="E13">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="H13">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>40.5</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>-0.5014526124883201</v>
+      </c>
+      <c r="E14">
+        <v>-0.4848049280043791</v>
+      </c>
+      <c r="F14">
+        <v>0.01664768448394099</v>
+      </c>
+      <c r="G14">
+        <v>-0.8680898766780916</v>
+      </c>
+      <c r="H14">
+        <v>-0.1281756999440235</v>
+      </c>
+      <c r="I14">
+        <v>0.739914176734068</v>
+      </c>
+      <c r="J14">
+        <v>32</v>
+      </c>
+      <c r="K14">
+        <v>0.4799286921459572</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15">
         <v>0.02839640640096549</v>
       </c>
-      <c r="E12">
+      <c r="E15">
         <v>0.02880153759533876</v>
       </c>
-      <c r="F12">
+      <c r="F15">
         <v>0.0004051311943732636</v>
       </c>
-      <c r="G12">
+      <c r="G15">
         <v>0.02772895183826347</v>
       </c>
-      <c r="H12">
+      <c r="H15">
         <v>0.02980166770487564</v>
       </c>
-      <c r="I12">
+      <c r="I15">
         <v>0.00207271586661217</v>
       </c>
-      <c r="J12">
+      <c r="J15">
         <v>35</v>
       </c>
-      <c r="K12">
+      <c r="K15">
         <v>0.6588432549492806</v>
       </c>
-      <c r="L12" t="b">
+      <c r="L15" t="b">
         <v>0</v>
       </c>
     </row>

--- a/result/xlsx/mannwhitney1.xlsx
+++ b/result/xlsx/mannwhitney1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>metric</t>
   </si>
@@ -64,12 +64,27 @@
     <t>RMS40_mkV</t>
   </si>
   <si>
+    <t>cwt_freq</t>
+  </si>
+  <si>
+    <t>cwt_time</t>
+  </si>
+  <si>
+    <t>dfa</t>
+  </si>
+  <si>
     <t>fQRS_ms</t>
   </si>
   <si>
     <t>kurtosis</t>
   </si>
   <si>
+    <t>max_psd_freq</t>
+  </si>
+  <si>
+    <t>max_psd_psd</t>
+  </si>
+  <si>
     <t>mean</t>
   </si>
   <si>
@@ -83,6 +98,9 @@
   </si>
   <si>
     <t>ratio_psd_power</t>
+  </si>
+  <si>
+    <t>sample_entropy</t>
   </si>
   <si>
     <t>shannon_entropy</t>
@@ -423,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -627,28 +645,28 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>34.24</v>
+        <v>390.6249999999999</v>
       </c>
       <c r="E6">
-        <v>37.92</v>
+        <v>390.6249999999999</v>
       </c>
       <c r="F6">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>56.55111111111111</v>
+        <v>398.5164141414141</v>
       </c>
       <c r="H6">
-        <v>38.84444444444444</v>
+        <v>390.6249999999999</v>
       </c>
       <c r="I6">
-        <v>-17.70666666666667</v>
+        <v>-7.891414141414145</v>
       </c>
       <c r="J6">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K6">
-        <v>0.5960519337626051</v>
+        <v>0.3740627974908824</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -665,31 +683,31 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>7.187757737805665</v>
+        <v>0.0590990990990991</v>
       </c>
       <c r="E7">
-        <v>2.537530552679585</v>
+        <v>0.04868868868868869</v>
       </c>
       <c r="F7">
-        <v>-4.65022718512608</v>
+        <v>-0.01041041041041041</v>
       </c>
       <c r="G7">
-        <v>6.460769981429733</v>
+        <v>0.08241130018907797</v>
       </c>
       <c r="H7">
-        <v>2.368048245966114</v>
+        <v>0.05413413413413413</v>
       </c>
       <c r="I7">
-        <v>-4.092721735463619</v>
+        <v>-0.02827716605494384</v>
       </c>
       <c r="J7">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="K7">
-        <v>0.003568628436933387</v>
+        <v>0.3632438165337984</v>
       </c>
       <c r="L7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -703,28 +721,28 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>-0.0001374879057452028</v>
+        <v>1.870263305875198</v>
       </c>
       <c r="E8">
-        <v>-0.00042075036407395</v>
+        <v>1.919659023244198</v>
       </c>
       <c r="F8">
-        <v>-0.0002832624583287473</v>
+        <v>0.04939571736900028</v>
       </c>
       <c r="G8">
-        <v>1.403217058176104E-05</v>
+        <v>1.744791571798233</v>
       </c>
       <c r="H8">
-        <v>-0.000949087641435614</v>
+        <v>1.930544804770661</v>
       </c>
       <c r="I8">
-        <v>-0.000963119812017375</v>
+        <v>0.1857532329724281</v>
       </c>
       <c r="J8">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="K8">
-        <v>0.1577043874630777</v>
+        <v>0.2163730080576375</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -741,28 +759,28 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>1.174853803563651</v>
+        <v>34.24</v>
       </c>
       <c r="E9">
-        <v>1.203740639847587</v>
+        <v>37.92</v>
       </c>
       <c r="F9">
-        <v>0.02888683628393629</v>
+        <v>3.68</v>
       </c>
       <c r="G9">
-        <v>1.320328930749395</v>
+        <v>56.55111111111111</v>
       </c>
       <c r="H9">
-        <v>1.266064137598739</v>
+        <v>38.84444444444444</v>
       </c>
       <c r="I9">
-        <v>-0.05426479315065591</v>
+        <v>-17.70666666666667</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K9">
-        <v>0.7239320396139757</v>
+        <v>0.5960519337626051</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -779,31 +797,31 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>-0.1264858932598404</v>
+        <v>7.187757737805665</v>
       </c>
       <c r="E10">
-        <v>-0.5966701504409082</v>
+        <v>2.537530552679585</v>
       </c>
       <c r="F10">
-        <v>-0.4701842571810678</v>
+        <v>-4.65022718512608</v>
       </c>
       <c r="G10">
-        <v>-0.1930557036416016</v>
+        <v>6.460769981429733</v>
       </c>
       <c r="H10">
-        <v>-0.356179393534465</v>
+        <v>2.368048245966114</v>
       </c>
       <c r="I10">
-        <v>-0.1631236898928634</v>
+        <v>-4.092721735463619</v>
       </c>
       <c r="J10">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="K10">
-        <v>0.5364994693194564</v>
+        <v>0.003568628436933387</v>
       </c>
       <c r="L10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -817,28 +835,28 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>0.001144086673244057</v>
+        <v>362.5</v>
       </c>
       <c r="E11">
-        <v>0.001881086486130078</v>
+        <v>337.5</v>
       </c>
       <c r="F11">
-        <v>0.000736999812886021</v>
+        <v>-25</v>
       </c>
       <c r="G11">
-        <v>0.08732116764256036</v>
+        <v>371.5277777777778</v>
       </c>
       <c r="H11">
-        <v>0.006471272250853074</v>
+        <v>334.7222222222222</v>
       </c>
       <c r="I11">
-        <v>-0.08084989539170728</v>
+        <v>-36.80555555555554</v>
       </c>
       <c r="J11">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="K11">
-        <v>0.331387096247615</v>
+        <v>0.4725238713350892</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -855,28 +873,28 @@
         <v>9</v>
       </c>
       <c r="D12">
-        <v>6.636005579377209E-05</v>
+        <v>2.055247385039394E-09</v>
       </c>
       <c r="E12">
-        <v>7.643116879641553E-06</v>
+        <v>5.900331929375982E-10</v>
       </c>
       <c r="F12">
-        <v>-5.871693891413054E-05</v>
+        <v>-1.465214192101796E-09</v>
       </c>
       <c r="G12">
-        <v>0.09534153771936786</v>
+        <v>1.019629324931943E-08</v>
       </c>
       <c r="H12">
-        <v>0.001385121457055902</v>
+        <v>2.070441211313914E-09</v>
       </c>
       <c r="I12">
-        <v>-0.09395641626231196</v>
+        <v>-8.125852038005513E-09</v>
       </c>
       <c r="J12">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K12">
-        <v>0.2893148323819877</v>
+        <v>0.331387096247615</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -893,28 +911,28 @@
         <v>9</v>
       </c>
       <c r="D13">
-        <v>9.965784284662087</v>
+        <v>-0.0001374879057452028</v>
       </c>
       <c r="E13">
-        <v>9.965784284662087</v>
+        <v>-0.00042075036407395</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>-0.0002832624583287473</v>
       </c>
       <c r="G13">
-        <v>9.965784284662087</v>
+        <v>1.403217058176104E-05</v>
       </c>
       <c r="H13">
-        <v>9.965784284662087</v>
+        <v>-0.000949087641435614</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>-0.000963119812017375</v>
       </c>
       <c r="J13">
-        <v>40.5</v>
+        <v>57</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0.1577043874630777</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -931,28 +949,28 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>-0.5014526124883201</v>
+        <v>1.174853803563651</v>
       </c>
       <c r="E14">
-        <v>-0.4848049280043791</v>
+        <v>1.203740639847587</v>
       </c>
       <c r="F14">
-        <v>0.01664768448394099</v>
+        <v>0.02888683628393629</v>
       </c>
       <c r="G14">
-        <v>-0.8680898766780916</v>
+        <v>1.320328930749395</v>
       </c>
       <c r="H14">
-        <v>-0.1281756999440235</v>
+        <v>1.266064137598739</v>
       </c>
       <c r="I14">
-        <v>0.739914176734068</v>
+        <v>-0.05426479315065591</v>
       </c>
       <c r="J14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K14">
-        <v>0.4799286921459572</v>
+        <v>0.7239320396139757</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -969,30 +987,258 @@
         <v>9</v>
       </c>
       <c r="D15">
+        <v>-0.1264858932598404</v>
+      </c>
+      <c r="E15">
+        <v>-0.5966701504409082</v>
+      </c>
+      <c r="F15">
+        <v>-0.4701842571810678</v>
+      </c>
+      <c r="G15">
+        <v>-0.1930557036416016</v>
+      </c>
+      <c r="H15">
+        <v>-0.356179393534465</v>
+      </c>
+      <c r="I15">
+        <v>-0.1631236898928634</v>
+      </c>
+      <c r="J15">
+        <v>48</v>
+      </c>
+      <c r="K15">
+        <v>0.5364994693194564</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>0.001144086673244057</v>
+      </c>
+      <c r="E16">
+        <v>0.001881086486130078</v>
+      </c>
+      <c r="F16">
+        <v>0.000736999812886021</v>
+      </c>
+      <c r="G16">
+        <v>0.08732116764256036</v>
+      </c>
+      <c r="H16">
+        <v>0.006471272250853074</v>
+      </c>
+      <c r="I16">
+        <v>-0.08084989539170728</v>
+      </c>
+      <c r="J16">
+        <v>29</v>
+      </c>
+      <c r="K16">
+        <v>0.331387096247615</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>6.636005579377209E-05</v>
+      </c>
+      <c r="E17">
+        <v>7.643116879641553E-06</v>
+      </c>
+      <c r="F17">
+        <v>-5.871693891413054E-05</v>
+      </c>
+      <c r="G17">
+        <v>0.09534153771936786</v>
+      </c>
+      <c r="H17">
+        <v>0.001385121457055902</v>
+      </c>
+      <c r="I17">
+        <v>-0.09395641626231196</v>
+      </c>
+      <c r="J17">
+        <v>53</v>
+      </c>
+      <c r="K17">
+        <v>0.2893148323819877</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>0.7116183354028598</v>
+      </c>
+      <c r="E18">
+        <v>0.7172168430400329</v>
+      </c>
+      <c r="F18">
+        <v>0.005598507637173067</v>
+      </c>
+      <c r="G18">
+        <v>0.685919129293855</v>
+      </c>
+      <c r="H18">
+        <v>0.7912065063786096</v>
+      </c>
+      <c r="I18">
+        <v>0.1052873770847546</v>
+      </c>
+      <c r="J18">
+        <v>34</v>
+      </c>
+      <c r="K18">
+        <v>0.5962416305866567</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="E19">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="H19">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>40.5</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <v>9</v>
+      </c>
+      <c r="D20">
+        <v>-0.5014526124883201</v>
+      </c>
+      <c r="E20">
+        <v>-0.4848049280043791</v>
+      </c>
+      <c r="F20">
+        <v>0.01664768448394099</v>
+      </c>
+      <c r="G20">
+        <v>-0.8680898766780916</v>
+      </c>
+      <c r="H20">
+        <v>-0.1281756999440235</v>
+      </c>
+      <c r="I20">
+        <v>0.739914176734068</v>
+      </c>
+      <c r="J20">
+        <v>32</v>
+      </c>
+      <c r="K20">
+        <v>0.4799286921459572</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21">
+        <v>9</v>
+      </c>
+      <c r="D21">
         <v>0.02839640640096549</v>
       </c>
-      <c r="E15">
+      <c r="E21">
         <v>0.02880153759533876</v>
       </c>
-      <c r="F15">
+      <c r="F21">
         <v>0.0004051311943732636</v>
       </c>
-      <c r="G15">
+      <c r="G21">
         <v>0.02772895183826347</v>
       </c>
-      <c r="H15">
+      <c r="H21">
         <v>0.02980166770487564</v>
       </c>
-      <c r="I15">
+      <c r="I21">
         <v>0.00207271586661217</v>
       </c>
-      <c r="J15">
+      <c r="J21">
         <v>35</v>
       </c>
-      <c r="K15">
+      <c r="K21">
         <v>0.6588432549492806</v>
       </c>
-      <c r="L15" t="b">
+      <c r="L21" t="b">
         <v>0</v>
       </c>
     </row>

--- a/result/xlsx/mannwhitney1.xlsx
+++ b/result/xlsx/mannwhitney1.xlsx
@@ -797,31 +797,31 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>7.187757737805665</v>
+        <v>7.976318079681183</v>
       </c>
       <c r="E10">
-        <v>2.537530552679585</v>
+        <v>6.857850732758875</v>
       </c>
       <c r="F10">
-        <v>-4.65022718512608</v>
+        <v>-1.118467346922309</v>
       </c>
       <c r="G10">
-        <v>6.460769981429733</v>
+        <v>7.751661565496856</v>
       </c>
       <c r="H10">
-        <v>2.368048245966114</v>
+        <v>5.998807656402229</v>
       </c>
       <c r="I10">
-        <v>-4.092721735463619</v>
+        <v>-1.752853909094627</v>
       </c>
       <c r="J10">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="K10">
-        <v>0.003568628436933387</v>
+        <v>0.1333202155896274</v>
       </c>
       <c r="L10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -911,28 +911,28 @@
         <v>9</v>
       </c>
       <c r="D13">
-        <v>-0.0001374879057452028</v>
+        <v>3.245736620707301E-05</v>
       </c>
       <c r="E13">
-        <v>-0.00042075036407395</v>
+        <v>2.802054242041337E-05</v>
       </c>
       <c r="F13">
-        <v>-0.0002832624583287473</v>
+        <v>-4.436823786659645E-06</v>
       </c>
       <c r="G13">
-        <v>1.403217058176104E-05</v>
+        <v>6.86186064216401E-05</v>
       </c>
       <c r="H13">
-        <v>-0.000949087641435614</v>
+        <v>1.376606966278328E-05</v>
       </c>
       <c r="I13">
-        <v>-0.000963119812017375</v>
+        <v>-5.485253675885682E-05</v>
       </c>
       <c r="J13">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K13">
-        <v>0.1577043874630777</v>
+        <v>0.5364994693194564</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -949,28 +949,28 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>1.174853803563651</v>
+        <v>1.202027697767326</v>
       </c>
       <c r="E14">
-        <v>1.203740639847587</v>
+        <v>1.17274572817694</v>
       </c>
       <c r="F14">
-        <v>0.02888683628393629</v>
+        <v>-0.02928196959038609</v>
       </c>
       <c r="G14">
-        <v>1.320328930749395</v>
+        <v>1.213565664170107</v>
       </c>
       <c r="H14">
-        <v>1.266064137598739</v>
+        <v>1.200458911275968</v>
       </c>
       <c r="I14">
-        <v>-0.05426479315065591</v>
+        <v>-0.01310675289413843</v>
       </c>
       <c r="J14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K14">
-        <v>0.7239320396139757</v>
+        <v>0.9296365245070707</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -1101,28 +1101,28 @@
         <v>9</v>
       </c>
       <c r="D18">
-        <v>0.7116183354028598</v>
+        <v>0.5626785779216068</v>
       </c>
       <c r="E18">
-        <v>0.7172168430400329</v>
+        <v>0.5794872787573536</v>
       </c>
       <c r="F18">
-        <v>0.005598507637173067</v>
+        <v>0.01680870083574681</v>
       </c>
       <c r="G18">
-        <v>0.685919129293855</v>
+        <v>0.6153553922528598</v>
       </c>
       <c r="H18">
-        <v>0.7912065063786096</v>
+        <v>0.660762852061841</v>
       </c>
       <c r="I18">
-        <v>0.1052873770847546</v>
+        <v>0.0454074598089812</v>
       </c>
       <c r="J18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K18">
-        <v>0.5962416305866567</v>
+        <v>0.7239320396139757</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1177,28 +1177,28 @@
         <v>9</v>
       </c>
       <c r="D20">
-        <v>-0.5014526124883201</v>
+        <v>0.4525371913262313</v>
       </c>
       <c r="E20">
-        <v>-0.4848049280043791</v>
+        <v>0.1229945835965955</v>
       </c>
       <c r="F20">
-        <v>0.01664768448394099</v>
+        <v>-0.3295426077296358</v>
       </c>
       <c r="G20">
-        <v>-0.8680898766780916</v>
+        <v>0.3435774446868992</v>
       </c>
       <c r="H20">
-        <v>-0.1281756999440235</v>
+        <v>0.1744727405697565</v>
       </c>
       <c r="I20">
-        <v>0.739914176734068</v>
+        <v>-0.1691047041171427</v>
       </c>
       <c r="J20">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K20">
-        <v>0.4799286921459572</v>
+        <v>0.6588432549492806</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1215,28 +1215,28 @@
         <v>9</v>
       </c>
       <c r="D21">
-        <v>0.02839640640096549</v>
+        <v>0.01564437683076316</v>
       </c>
       <c r="E21">
-        <v>0.02880153759533876</v>
+        <v>0.008454296271040681</v>
       </c>
       <c r="F21">
-        <v>0.0004051311943732636</v>
+        <v>-0.007190080559722483</v>
       </c>
       <c r="G21">
-        <v>0.02772895183826347</v>
+        <v>0.01374865536968189</v>
       </c>
       <c r="H21">
-        <v>0.02980166770487564</v>
+        <v>0.009009773062333207</v>
       </c>
       <c r="I21">
-        <v>0.00207271586661217</v>
+        <v>-0.004738882307348679</v>
       </c>
       <c r="J21">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="K21">
-        <v>0.6588432549492806</v>
+        <v>0.1119613542637483</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>

--- a/result/xlsx/mannwhitney1.xlsx
+++ b/result/xlsx/mannwhitney1.xlsx
@@ -496,25 +496,25 @@
         <v>79.68000000000001</v>
       </c>
       <c r="E2">
-        <v>71.36000000000001</v>
+        <v>70.56</v>
       </c>
       <c r="F2">
-        <v>-8.319999999999993</v>
+        <v>-9.120000000000005</v>
       </c>
       <c r="G2">
-        <v>100.5688888888889</v>
+        <v>98.43555555555555</v>
       </c>
       <c r="H2">
-        <v>73.19111111111111</v>
+        <v>73.15555555555555</v>
       </c>
       <c r="I2">
-        <v>-27.37777777777778</v>
+        <v>-25.28</v>
       </c>
       <c r="J2">
-        <v>57.5</v>
+        <v>58</v>
       </c>
       <c r="K2">
-        <v>0.1449127807467187</v>
+        <v>0.1333202155896274</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
@@ -534,25 +534,25 @@
         <v>497</v>
       </c>
       <c r="E3">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="F3">
-        <v>-52</v>
+        <v>-57</v>
       </c>
       <c r="G3">
-        <v>627.5555555555555</v>
+        <v>614.2222222222222</v>
       </c>
       <c r="H3">
-        <v>456.4444444444445</v>
+        <v>456.2222222222222</v>
       </c>
       <c r="I3">
-        <v>-171.1111111111111</v>
+        <v>-157.9999999999999</v>
       </c>
       <c r="J3">
-        <v>57.5</v>
+        <v>58</v>
       </c>
       <c r="K3">
-        <v>0.1449127807467187</v>
+        <v>0.1333202155896274</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
@@ -569,28 +569,28 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E4">
         <v>259</v>
       </c>
       <c r="F4">
-        <v>-22</v>
+        <v>-18</v>
       </c>
       <c r="G4">
-        <v>274.1111111111111</v>
+        <v>246.3333333333333</v>
       </c>
       <c r="H4">
         <v>213.6666666666667</v>
       </c>
       <c r="I4">
-        <v>-60.44444444444443</v>
+        <v>-32.66666666666669</v>
       </c>
       <c r="J4">
-        <v>59.5</v>
+        <v>52</v>
       </c>
       <c r="K4">
-        <v>0.1019907052411099</v>
+        <v>0.3308875570965121</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
@@ -607,22 +607,22 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>0.02952097900191285</v>
+        <v>0.02963373570230184</v>
       </c>
       <c r="E5">
-        <v>0.016144306175159</v>
+        <v>0.01608519684500757</v>
       </c>
       <c r="F5">
-        <v>-0.01337667282675385</v>
+        <v>-0.01354853885729428</v>
       </c>
       <c r="G5">
-        <v>0.0216162816877965</v>
+        <v>0.02161726091033362</v>
       </c>
       <c r="H5">
-        <v>0.0171095183354517</v>
+        <v>0.01714518353702889</v>
       </c>
       <c r="I5">
-        <v>-0.0045067633523448</v>
+        <v>-0.004472077373304736</v>
       </c>
       <c r="J5">
         <v>46</v>
@@ -721,22 +721,22 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>1.870263305875198</v>
+        <v>1.869646772855092</v>
       </c>
       <c r="E8">
-        <v>1.919659023244198</v>
+        <v>1.919249747006841</v>
       </c>
       <c r="F8">
-        <v>0.04939571736900028</v>
+        <v>0.04960297415174897</v>
       </c>
       <c r="G8">
-        <v>1.744791571798233</v>
+        <v>1.746461800538449</v>
       </c>
       <c r="H8">
-        <v>1.930544804770661</v>
+        <v>1.929986471106661</v>
       </c>
       <c r="I8">
-        <v>0.1857532329724281</v>
+        <v>0.1835246705682125</v>
       </c>
       <c r="J8">
         <v>26</v>
@@ -768,13 +768,13 @@
         <v>3.68</v>
       </c>
       <c r="G9">
-        <v>56.55111111111111</v>
+        <v>58.86222222222222</v>
       </c>
       <c r="H9">
-        <v>38.84444444444444</v>
+        <v>38.80888888888889</v>
       </c>
       <c r="I9">
-        <v>-17.70666666666667</v>
+        <v>-20.05333333333333</v>
       </c>
       <c r="J9">
         <v>47</v>
@@ -797,28 +797,28 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>7.976318079681183</v>
+        <v>7.947747306009594</v>
       </c>
       <c r="E10">
-        <v>6.857850732758875</v>
+        <v>6.726899775548087</v>
       </c>
       <c r="F10">
-        <v>-1.118467346922309</v>
+        <v>-1.220847530461507</v>
       </c>
       <c r="G10">
-        <v>7.751661565496856</v>
+        <v>7.805450771105945</v>
       </c>
       <c r="H10">
-        <v>5.998807656402229</v>
+        <v>6.024352713428733</v>
       </c>
       <c r="I10">
-        <v>-1.752853909094627</v>
+        <v>-1.781098057677212</v>
       </c>
       <c r="J10">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K10">
-        <v>0.1333202155896274</v>
+        <v>0.1119613542637483</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -838,25 +838,25 @@
         <v>362.5</v>
       </c>
       <c r="E11">
-        <v>337.5</v>
+        <v>318.75</v>
       </c>
       <c r="F11">
-        <v>-25</v>
+        <v>-43.75</v>
       </c>
       <c r="G11">
-        <v>371.5277777777778</v>
+        <v>389.5833333333333</v>
       </c>
       <c r="H11">
-        <v>334.7222222222222</v>
+        <v>331.9444444444445</v>
       </c>
       <c r="I11">
-        <v>-36.80555555555554</v>
+        <v>-57.63888888888886</v>
       </c>
       <c r="J11">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K11">
-        <v>0.4725238713350892</v>
+        <v>0.4184922334468199</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -873,22 +873,22 @@
         <v>9</v>
       </c>
       <c r="D12">
-        <v>2.055247385039394E-09</v>
+        <v>2.340759465174268E-09</v>
       </c>
       <c r="E12">
-        <v>5.900331929375982E-10</v>
+        <v>5.540800703841373E-10</v>
       </c>
       <c r="F12">
-        <v>-1.465214192101796E-09</v>
+        <v>-1.786679394790131E-09</v>
       </c>
       <c r="G12">
-        <v>1.019629324931943E-08</v>
+        <v>9.884770542217217E-09</v>
       </c>
       <c r="H12">
-        <v>2.070441211313914E-09</v>
+        <v>2.258190468605126E-09</v>
       </c>
       <c r="I12">
-        <v>-8.125852038005513E-09</v>
+        <v>-7.626580073612091E-09</v>
       </c>
       <c r="J12">
         <v>52</v>
@@ -911,28 +911,28 @@
         <v>9</v>
       </c>
       <c r="D13">
-        <v>3.245736620707301E-05</v>
+        <v>3.351584354836885E-05</v>
       </c>
       <c r="E13">
-        <v>2.802054242041337E-05</v>
+        <v>2.540957763764956E-05</v>
       </c>
       <c r="F13">
-        <v>-4.436823786659645E-06</v>
+        <v>-8.106265910719289E-06</v>
       </c>
       <c r="G13">
-        <v>6.86186064216401E-05</v>
+        <v>7.365251474210952E-05</v>
       </c>
       <c r="H13">
-        <v>1.376606966278328E-05</v>
+        <v>1.325217798709094E-05</v>
       </c>
       <c r="I13">
-        <v>-5.485253675885682E-05</v>
+        <v>-6.040033675501858E-05</v>
       </c>
       <c r="J13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K13">
-        <v>0.5364994693194564</v>
+        <v>0.4799286921459572</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -949,28 +949,28 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>1.202027697767326</v>
+        <v>1.192935124537182</v>
       </c>
       <c r="E14">
-        <v>1.17274572817694</v>
+        <v>1.197657566408511</v>
       </c>
       <c r="F14">
-        <v>-0.02928196959038609</v>
+        <v>0.004722441871329197</v>
       </c>
       <c r="G14">
-        <v>1.213565664170107</v>
+        <v>1.209293802231381</v>
       </c>
       <c r="H14">
-        <v>1.200458911275968</v>
+        <v>1.197212614868032</v>
       </c>
       <c r="I14">
-        <v>-0.01310675289413843</v>
+        <v>-0.01208118736334951</v>
       </c>
       <c r="J14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K14">
-        <v>0.9296365245070707</v>
+        <v>1</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -987,22 +987,22 @@
         <v>9</v>
       </c>
       <c r="D15">
-        <v>-0.1264858932598404</v>
+        <v>-0.1266302694550845</v>
       </c>
       <c r="E15">
-        <v>-0.5966701504409082</v>
+        <v>-0.6048480201138513</v>
       </c>
       <c r="F15">
-        <v>-0.4701842571810678</v>
+        <v>-0.4782177506587668</v>
       </c>
       <c r="G15">
-        <v>-0.1930557036416016</v>
+        <v>-0.2429207361735717</v>
       </c>
       <c r="H15">
-        <v>-0.356179393534465</v>
+        <v>-0.3644488146541777</v>
       </c>
       <c r="I15">
-        <v>-0.1631236898928634</v>
+        <v>-0.121528078480606</v>
       </c>
       <c r="J15">
         <v>48</v>
@@ -1025,22 +1025,22 @@
         <v>9</v>
       </c>
       <c r="D16">
-        <v>0.001144086673244057</v>
+        <v>0.001145382160993332</v>
       </c>
       <c r="E16">
-        <v>0.001881086486130078</v>
+        <v>0.001869497199871253</v>
       </c>
       <c r="F16">
-        <v>0.000736999812886021</v>
+        <v>0.0007241150388779208</v>
       </c>
       <c r="G16">
-        <v>0.08732116764256036</v>
+        <v>0.08696654962070943</v>
       </c>
       <c r="H16">
-        <v>0.006471272250853074</v>
+        <v>0.006680084737557798</v>
       </c>
       <c r="I16">
-        <v>-0.08084989539170728</v>
+        <v>-0.08028646488315164</v>
       </c>
       <c r="J16">
         <v>29</v>
@@ -1063,22 +1063,22 @@
         <v>9</v>
       </c>
       <c r="D17">
-        <v>6.636005579377209E-05</v>
+        <v>7.117634993294828E-05</v>
       </c>
       <c r="E17">
-        <v>7.643116879641553E-06</v>
+        <v>6.792161775086165E-06</v>
       </c>
       <c r="F17">
-        <v>-5.871693891413054E-05</v>
+        <v>-6.438418815786212E-05</v>
       </c>
       <c r="G17">
-        <v>0.09534153771936786</v>
+        <v>0.09644101046580997</v>
       </c>
       <c r="H17">
-        <v>0.001385121457055902</v>
+        <v>0.001332775190860223</v>
       </c>
       <c r="I17">
-        <v>-0.09395641626231196</v>
+        <v>-0.09510823527494974</v>
       </c>
       <c r="J17">
         <v>53</v>
@@ -1101,28 +1101,28 @@
         <v>9</v>
       </c>
       <c r="D18">
-        <v>0.5626785779216068</v>
+        <v>0.5627988840550237</v>
       </c>
       <c r="E18">
-        <v>0.5794872787573536</v>
+        <v>0.5949984252349811</v>
       </c>
       <c r="F18">
-        <v>0.01680870083574681</v>
+        <v>0.03219954117995749</v>
       </c>
       <c r="G18">
-        <v>0.6153553922528598</v>
+        <v>0.6151607364321575</v>
       </c>
       <c r="H18">
-        <v>0.660762852061841</v>
+        <v>0.6635841193022508</v>
       </c>
       <c r="I18">
-        <v>0.0454074598089812</v>
+        <v>0.04842338287009329</v>
       </c>
       <c r="J18">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18">
-        <v>0.7239320396139757</v>
+        <v>0.7910815129207817</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1177,28 +1177,28 @@
         <v>9</v>
       </c>
       <c r="D20">
-        <v>0.4525371913262313</v>
+        <v>0.4503567774359132</v>
       </c>
       <c r="E20">
-        <v>0.1229945835965955</v>
+        <v>0.08471663802105557</v>
       </c>
       <c r="F20">
-        <v>-0.3295426077296358</v>
+        <v>-0.3656401394148577</v>
       </c>
       <c r="G20">
-        <v>0.3435774446868992</v>
+        <v>0.3957956083760682</v>
       </c>
       <c r="H20">
-        <v>0.1744727405697565</v>
+        <v>0.1423037634014709</v>
       </c>
       <c r="I20">
-        <v>-0.1691047041171427</v>
+        <v>-0.2534918449745973</v>
       </c>
       <c r="J20">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K20">
-        <v>0.6588432549492806</v>
+        <v>0.5364994693194564</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1215,28 +1215,28 @@
         <v>9</v>
       </c>
       <c r="D21">
-        <v>0.01564437683076316</v>
+        <v>0.01570221039507413</v>
       </c>
       <c r="E21">
-        <v>0.008454296271040681</v>
+        <v>0.00843003356359719</v>
       </c>
       <c r="F21">
-        <v>-0.007190080559722483</v>
+        <v>-0.007272176831476945</v>
       </c>
       <c r="G21">
-        <v>0.01374865536968189</v>
+        <v>0.01379349528623104</v>
       </c>
       <c r="H21">
-        <v>0.009009773062333207</v>
+        <v>0.00899472573248584</v>
       </c>
       <c r="I21">
-        <v>-0.004738882307348679</v>
+        <v>-0.004798769553745204</v>
       </c>
       <c r="J21">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K21">
-        <v>0.1119613542637483</v>
+        <v>0.09339767452879261</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
